--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1675,6 +1675,210 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121656320</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58213</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334149</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6529568</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121656353</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>334045</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6529581</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121656320</v>
+        <v>121656353</v>
       </c>
       <c r="B10" t="n">
-        <v>58213</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334149</v>
+        <v>334045</v>
       </c>
       <c r="R10" t="n">
-        <v>6529568</v>
+        <v>6529581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656353</v>
+        <v>121656320</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>58216</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,25 +1791,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334045</v>
+        <v>334149</v>
       </c>
       <c r="R11" t="n">
-        <v>6529581</v>
+        <v>6529568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121656353</v>
+        <v>121656320</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>58216</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334045</v>
+        <v>334149</v>
       </c>
       <c r="R10" t="n">
-        <v>6529581</v>
+        <v>6529568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656320</v>
+        <v>121656353</v>
       </c>
       <c r="B11" t="n">
-        <v>58216</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,25 +1791,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334149</v>
+        <v>334045</v>
       </c>
       <c r="R11" t="n">
-        <v>6529568</v>
+        <v>6529581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121656320</v>
+        <v>121656353</v>
       </c>
       <c r="B10" t="n">
-        <v>58216</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334149</v>
+        <v>334045</v>
       </c>
       <c r="R10" t="n">
-        <v>6529568</v>
+        <v>6529581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656353</v>
+        <v>121656320</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>58216</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,25 +1791,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334045</v>
+        <v>334149</v>
       </c>
       <c r="R11" t="n">
-        <v>6529581</v>
+        <v>6529568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121656320</v>
+        <v>121656353</v>
       </c>
       <c r="B10" t="n">
-        <v>58216</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334149</v>
+        <v>334045</v>
       </c>
       <c r="R10" t="n">
-        <v>6529568</v>
+        <v>6529581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656353</v>
+        <v>121656320</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>58224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,25 +1791,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334045</v>
+        <v>334149</v>
       </c>
       <c r="R11" t="n">
-        <v>6529581</v>
+        <v>6529568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1680,7 +1680,7 @@
         <v>121656353</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -1680,7 +1680,7 @@
         <v>121656353</v>
       </c>
       <c r="B10" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>109819792</v>
       </c>
       <c r="B2" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -735,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334289.1985600573</v>
+        <v>334289</v>
       </c>
       <c r="R2" t="n">
-        <v>6529677.063748747</v>
+        <v>6529677</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -807,45 +802,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109819790</v>
+        <v>109819794</v>
       </c>
       <c r="B3" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102976</v>
+        <v>100054</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Falco peregrinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Tunstall, 1771</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -855,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334289.1985600573</v>
+        <v>334289</v>
       </c>
       <c r="R3" t="n">
-        <v>6529677.063748747</v>
+        <v>6529677</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -927,32 +921,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109819804</v>
+        <v>110234243</v>
       </c>
       <c r="B4" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,18 +951,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -983,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334289.1985600573</v>
+        <v>334294</v>
       </c>
       <c r="R4" t="n">
-        <v>6529677.063748747</v>
+        <v>6529666</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,22 +1002,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,32 +1044,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109819800</v>
+        <v>112331854</v>
       </c>
       <c r="B5" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1090,34 +1074,34 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtsfors, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334289.1985600573</v>
+        <v>334255</v>
       </c>
       <c r="R5" t="n">
-        <v>6529677.063748747</v>
+        <v>6529759</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,22 +1125,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,7 +1145,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Dahlén</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1183,37 +1157,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110234249</v>
+        <v>110234245</v>
       </c>
       <c r="B6" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1229,7 +1198,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334294.4265263509</v>
+        <v>334294</v>
       </c>
       <c r="R6" t="n">
-        <v>6529665.967432996</v>
+        <v>6529666</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1274,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,19 +1280,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110234242</v>
+        <v>109819790</v>
       </c>
       <c r="B7" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1344,16 +1308,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1363,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334294.4265263509</v>
+        <v>334289</v>
       </c>
       <c r="R7" t="n">
-        <v>6529665.967432996</v>
+        <v>6529677</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1393,22 +1353,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,49 +1395,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109819794</v>
+        <v>110234242</v>
       </c>
       <c r="B8" t="n">
-        <v>56437</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100054</v>
+        <v>102976</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Falco peregrinus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tunstall, 1771</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1487,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334289.1985600573</v>
+        <v>334294</v>
       </c>
       <c r="R8" t="n">
-        <v>6529677.063748747</v>
+        <v>6529666</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1517,22 +1472,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,37 +1514,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112331854</v>
+        <v>109819796</v>
       </c>
       <c r="B9" t="n">
-        <v>55816</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>102980</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1598,30 +1548,26 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334255</v>
+        <v>334289</v>
       </c>
       <c r="R9" t="n">
-        <v>6529758</v>
+        <v>6529677</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1645,12 +1591,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,7 +1621,7 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Dahlén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1677,53 +1633,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121656353</v>
+        <v>109819804</v>
       </c>
       <c r="B10" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334045</v>
+        <v>334289</v>
       </c>
       <c r="R10" t="n">
-        <v>6529581</v>
+        <v>6529677</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1747,12 +1714,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,27 +1744,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Anna Dahlén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Enviro Planning, Pia Edfors, Anders Esplund, Sofia Berg</t>
+          <t>Anna Dahlén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656320</v>
+        <v>110234249</v>
       </c>
       <c r="B11" t="n">
-        <v>58224</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,37 +1767,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>102995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334149</v>
+        <v>334294</v>
       </c>
       <c r="R11" t="n">
-        <v>6529568</v>
+        <v>6529666</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,12 +1837,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,15 +1867,257 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Anna Dahlén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Pia Edfors, Enviro Planning</t>
+          <t>Anna Dahlén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>109819800</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bengtsfors, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>334289</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6529677</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna Dahlén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna Dahlén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110234253</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bengtsfors, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>334294</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6529666</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Dahlén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Dahlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63067-2021 artfynd.xlsx
+++ b/artfynd/A 63067-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819792</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,6 +1174,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112331854</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819790</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1511,6 +1546,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234242</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819796</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1753,6 +1798,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819804</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1876,6 +1926,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234249</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1999,6 +2054,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819800</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2118,8 +2178,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>